--- a/AAII_Financials/Yearly/DE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DE_YR_FIN.xlsx
@@ -2226,7 +2226,7 @@
         <v>321000</v>
       </c>
       <c r="G42" s="3">
-        <v>61000</v>
+        <v>368000</v>
       </c>
       <c r="H42" s="3">
         <v>242000</v>
@@ -2379,7 +2379,7 @@
         <v>742000</v>
       </c>
       <c r="G45" s="3">
-        <v>373000</v>
+        <v>66000</v>
       </c>
       <c r="H45" s="3">
         <v>36000</v>
